--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104539_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104539_W9.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9855</v>
+        <v>3.7811</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3477</v>
+        <v>4.2312</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3622</v>
+        <v>-0.4501</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0389</v>
+        <v>7.0211</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3447</v>
+        <v>3.3486</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6942</v>
+        <v>3.6724</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3451</v>
+        <v>5.2964</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0838</v>
+        <v>3.0523</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6938</v>
+        <v>1.7247</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0833</v>
+        <v>1.1046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2388</v>
+        <v>-1.4189</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3266</v>
+        <v>-0.3743</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9122</v>
+        <v>-1.0446</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3884</v>
+        <v>2.7324</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0075</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3808</v>
+        <v>2.0404</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1047</v>
+        <v>2.8054</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6968</v>
+        <v>1.5676</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4079</v>
+        <v>1.2378</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7068</v>
+        <v>1.1244</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8485</v>
+        <v>0.8791</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8583</v>
+        <v>0.2453</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3979</v>
+        <v>1.681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.6886</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>0.9925</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>2.484</v>
+        <v>-0.9835</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3157</v>
+        <v>-0.4324</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1683</v>
+        <v>-0.5512</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2784</v>
+        <v>2.0505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1651</v>
+        <v>1.0478</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1133</v>
+        <v>1.0027</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7977</v>
+        <v>2.1215</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5582</v>
+        <v>1.7055</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2395</v>
+        <v>0.416</v>
       </c>
       <c r="J4" t="n">
-        <v>1.139</v>
+        <v>1.7011</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8832</v>
+        <v>0.8446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2558</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6587</v>
+        <v>0.4204</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6751</v>
+        <v>0.8609</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9837</v>
+        <v>-0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4266</v>
+        <v>1.1371</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9739</v>
+        <v>0.3758</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4528</v>
+        <v>0.7612</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.918</v>
+        <v>1.5946</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0186</v>
+        <v>2.0624</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1006</v>
+        <v>-0.4679</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7648</v>
+        <v>3.7777</v>
       </c>
       <c r="H5" t="n">
-        <v>3.261</v>
+        <v>3.268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5038</v>
+        <v>0.5097</v>
       </c>
       <c r="J5" t="n">
-        <v>3.305</v>
+        <v>3.286</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8226</v>
+        <v>2.8096</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4598</v>
+        <v>0.4917</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.342</v>
+        <v>-1.6871</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.7667</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5072</v>
+        <v>-0.9204</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8031</v>
+        <v>0.8035</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7328</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0703</v>
+        <v>-0.0941</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9975</v>
+        <v>2.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1601</v>
+        <v>2.1625</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1626</v>
+        <v>-0.1592</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4019</v>
+        <v>2.3869</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4044</v>
+        <v>-0.3836</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5819</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>-0.5089</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1137</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7137</v>
+        <v>-0.0458</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2564</v>
+        <v>-1.6773</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5427</v>
+        <v>1.6315</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.8666</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0275</v>
+        <v>-0.0205</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5608</v>
+        <v>-1.5725</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6883</v>
+        <v>0.7058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5178</v>
+        <v>0.1348</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>-0.1048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1778</v>
+        <v>0.2396</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4498</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7987</v>
+        <v>-1.0443</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3513</v>
+        <v>-2.0348</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5526</v>
+        <v>0.9905</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1873</v>
+        <v>-2.1951</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4702</v>
+        <v>-1.4787</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.717</v>
+        <v>-0.7165</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7265</v>
+        <v>-2.7591</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.4599</v>
+        <v>-2.4831</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5392</v>
+        <v>0.5639</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1352</v>
+        <v>-0.0964</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3902</v>
+        <v>-0.2466</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.255</v>
+        <v>0.1503</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8586</v>
+        <v>-1.115</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5747</v>
+        <v>-0.2468</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2839</v>
+        <v>-0.8682</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8895</v>
+        <v>0.9009</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0005</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8983</v>
+        <v>0.9014</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6906</v>
+        <v>1.6698</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6203</v>
+        <v>-0.6313</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3109</v>
+        <v>2.301</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8011</v>
+        <v>-0.7689</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6115</v>
+        <v>0.6308</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4947</v>
+        <v>-0.7687</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5904</v>
+        <v>-0.2179</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2117</v>
+        <v>-4.0368</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8838</v>
+        <v>-3.181</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3279</v>
+        <v>-0.8558</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0561</v>
+        <v>0.051</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7199</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.6753</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1877</v>
+        <v>-0.2263</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3121</v>
+        <v>-0.3362</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2439</v>
+        <v>0.2773</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7312</v>
+        <v>-1.5352</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6133</v>
+        <v>-1.1818</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1802</v>
+        <v>-4.7555</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6267</v>
+        <v>-4.1853</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5535</v>
+        <v>-0.5702</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1419</v>
+        <v>-0.123</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4818</v>
+        <v>0.4934</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6237</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.046</v>
+        <v>0.0286</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2007</v>
+        <v>0.1929</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1879</v>
+        <v>-0.1516</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2811</v>
+        <v>0.3005</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.469</v>
+        <v>-0.4521</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1971</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0434</v>
+        <v>-0.5718</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1537</v>
+        <v>-0.2201</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3895000000000008</v>
+        <v>-0.03530000000000033</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4212</v>
+        <v>-2.394099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0316</v>
+        <v>2.3588</v>
       </c>
       <c r="G12" t="n">
-        <v>15.4475</v>
+        <v>15.4962</v>
       </c>
       <c r="H12" t="n">
-        <v>11.716</v>
+        <v>11.7722</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7316</v>
+        <v>3.7237</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1594</v>
+        <v>10.9353</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2829</v>
+        <v>5.1756</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8765</v>
+        <v>5.759600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>4.288200000000001</v>
+        <v>4.5607</v>
       </c>
       <c r="N12" t="n">
-        <v>6.433000000000001</v>
+        <v>6.5968</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1448</v>
+        <v>-2.036</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.805000000000001</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.1466</v>
+        <v>-18.2106</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.9109</v>
+        <v>-6.5949</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8861</v>
+        <v>-3.5339</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0248</v>
+        <v>-3.0612</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1211</v>
+        <v>-2.1075</v>
       </c>
       <c r="W12" t="n">
-        <v>8.452299999999999</v>
+        <v>8.415100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.5735</v>
+        <v>-10.5227</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3461</v>
+        <v>4.5266</v>
       </c>
       <c r="E13" t="n">
-        <v>5.882</v>
+        <v>4.904</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.3775</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2302</v>
+        <v>-0.2466</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1022</v>
+        <v>-0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.128</v>
+        <v>-0.1297</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5069</v>
+        <v>1.4714</v>
       </c>
       <c r="K13" t="n">
-        <v>0.654</v>
+        <v>0.6303</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7371</v>
+        <v>-1.718</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>2.376</v>
+        <v>1.5651</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1897</v>
+        <v>1.2537</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1863</v>
+        <v>0.3115</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3624</v>
+        <v>3.6008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7279</v>
+        <v>0.8284</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6346</v>
+        <v>2.7724</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3254</v>
+        <v>2.3232</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6595</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6659</v>
+        <v>1.6654</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4699</v>
+        <v>0.4569</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8555</v>
+        <v>1.8663</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2582</v>
+        <v>1.2634</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1712</v>
+        <v>0.4158</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1282</v>
+        <v>-0.0044</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2605</v>
+        <v>3.3905</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1358</v>
+        <v>1.4851</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3962</v>
+        <v>1.9054</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9073</v>
+        <v>1.9023</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2324</v>
+        <v>2.2208</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3251</v>
+        <v>-0.3185</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7999</v>
+        <v>1.7672</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0292</v>
+        <v>2.006</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1074</v>
+        <v>0.1351</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1854</v>
+        <v>0.9372</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1644</v>
+        <v>0.4918</v>
       </c>
       <c r="U15" t="n">
-        <v>0.979</v>
+        <v>0.4454</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0902</v>
+        <v>1.5177</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3143</v>
+        <v>0.4285</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7759</v>
+        <v>1.0892</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4266</v>
+        <v>-4.9365</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4083</v>
+        <v>-5.6081</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0183</v>
+        <v>0.6716</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4418</v>
+        <v>-2.8593</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6203</v>
+        <v>-4.0279</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1785</v>
+        <v>1.1686</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9848</v>
+        <v>-2.0772</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.788</v>
+        <v>-1.5802</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1967</v>
+        <v>-0.497</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4952</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0217</v>
+        <v>1.6199</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7561</v>
+        <v>0.6614</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2655</v>
+        <v>0.9584</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.2896</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.9026</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8187</v>
+        <v>1.0453</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3326</v>
+        <v>0.1748</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1513</v>
+        <v>0.8704</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.9112</v>
+        <v>-2.4294</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.5882</v>
+        <v>-1.4074</v>
       </c>
       <c r="I17" t="n">
-        <v>0.677</v>
+        <v>-1.022</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.8119</v>
+        <v>-0.4681</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.9979</v>
+        <v>-0.6313</v>
       </c>
       <c r="L17" t="n">
-        <v>1.186</v>
+        <v>0.1632</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0993</v>
+        <v>-1.9613</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5903</v>
+        <v>-0.7761</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.509</v>
+        <v>-1.1852</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.881</v>
+        <v>0.9707</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1693</v>
+        <v>0.6429</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0504</v>
+        <v>0.3278</v>
       </c>
       <c r="V17" t="n">
-        <v>5.3026</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.917</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4639</v>
+        <v>-0.1303</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3722</v>
+        <v>-1.2162</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8361</v>
+        <v>1.0859</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9601</v>
+        <v>-1.952</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.531</v>
+        <v>-1.5308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4291</v>
+        <v>-0.4212</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.663</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5857</v>
+        <v>-0.5968</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2971</v>
+        <v>-1.2731</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>1.129</v>
+        <v>0.5258</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2642</v>
+        <v>0.4431</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1352</v>
+        <v>0.0827</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3973</v>
+        <v>-0.4597</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3631</v>
+        <v>-1.2412</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9657</v>
+        <v>0.7815</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6934</v>
+        <v>-1.4769</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9379</v>
+        <v>-0.4253</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6313</v>
+        <v>-1.0516</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0292</v>
+        <v>-0.3906</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7171</v>
+        <v>-0.1519</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7463</v>
+        <v>-0.2388</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6641</v>
+        <v>-1.0863</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2734</v>
       </c>
       <c r="O19" t="n">
-        <v>0.885</v>
+        <v>-0.8129</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2949</v>
+        <v>0.7896</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4869</v>
+        <v>0.2876</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.5021</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0668</v>
+        <v>-0.5493</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6966</v>
+        <v>-2.376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6298</v>
+        <v>1.8267</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4829</v>
+        <v>0.6994</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4301</v>
+        <v>-0.9364</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0529</v>
+        <v>1.6358</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.375</v>
+        <v>0.024</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1456</v>
+        <v>-0.7207</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2293</v>
+        <v>0.7447</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.108</v>
+        <v>0.6754</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2844</v>
+        <v>-0.2157</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8236</v>
+        <v>0.8911</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1893</v>
+        <v>0.1383</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1875</v>
+        <v>-0.4879</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3768</v>
+        <v>0.6262</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7677</v>
+        <v>-1.5063</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6541</v>
+        <v>-0.319</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1135</v>
+        <v>-1.1872</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7513</v>
+        <v>-2.7443</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1169</v>
+        <v>-2.1113</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6344</v>
+        <v>-0.633</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2547</v>
+        <v>-0.2643</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4966</v>
+        <v>-2.48</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2017</v>
+        <v>0.0591</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7026</v>
+        <v>0.6099</v>
       </c>
       <c r="V21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8461</v>
+        <v>-2.797</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5417</v>
+        <v>1.3419</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3877</v>
+        <v>-4.1389</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9768</v>
+        <v>-1.9792</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.111</v>
+        <v>-0.1174</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8658</v>
+        <v>-1.8618</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9911</v>
+        <v>-1.0072</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2047</v>
+        <v>-0.2176</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9858</v>
+        <v>-0.972</v>
       </c>
       <c r="N22" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>1.25</v>
+        <v>0.2914</v>
       </c>
       <c r="T22" t="n">
-        <v>1.733</v>
+        <v>0.5571</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.483</v>
+        <v>-0.2658</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.5994</v>
+        <v>-3.584</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8796</v>
+        <v>-4.1057</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9507</v>
+        <v>-2.0368</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0711</v>
+        <v>-2.0688</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0612</v>
+        <v>-1.5815</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0403</v>
+        <v>-0.3527</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.021</v>
+        <v>-1.2288</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.8377</v>
+        <v>0.2496</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.3071</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5306</v>
+        <v>0.1708</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2236</v>
+        <v>-1.831</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2669</v>
+        <v>-0.4314</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4904</v>
+        <v>-1.3997</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2743</v>
+        <v>-0.3845</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0212</v>
+        <v>-0.3256</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2531</v>
+        <v>-0.0589</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9949</v>
+        <v>-4.1489</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9924</v>
+        <v>-4.3321</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0025</v>
+        <v>0.1832</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5733</v>
+        <v>-3.0744</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3418</v>
+        <v>-2.0447</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2315</v>
+        <v>-1.0297</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2811</v>
+        <v>-2.8615</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0999</v>
+        <v>-2.3172</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1812</v>
+        <v>-0.5443</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8543</v>
+        <v>-0.2129</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4417</v>
+        <v>0.2725</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4126</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2894</v>
+        <v>0.015</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3266</v>
+        <v>-0.3324</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0372</v>
+        <v>0.3474</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7712</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3894000000000015</v>
+        <v>0.3836999999999993</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.031600000000001</v>
+        <v>-2.358599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4212</v>
+        <v>2.7423</v>
       </c>
       <c r="G25" t="n">
-        <v>-15.4475</v>
+        <v>-15.4959</v>
       </c>
       <c r="H25" t="n">
-        <v>-11.7158</v>
+        <v>-11.7724</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.7319</v>
+        <v>-3.7235</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2882</v>
+        <v>-4.5608</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.4329</v>
+        <v>-6.5969</v>
       </c>
       <c r="L25" t="n">
-        <v>2.1449</v>
+        <v>2.0359</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.1596</v>
+        <v>-10.935</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.282800000000001</v>
+        <v>-5.1755</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.8764</v>
+        <v>-5.7597</v>
       </c>
       <c r="P25" t="n">
-        <v>6.804900000000001</v>
+        <v>6.828799999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3418</v>
+        <v>-11.3818</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S25" t="n">
-        <v>6.9109</v>
+        <v>6.9434</v>
       </c>
       <c r="T25" t="n">
-        <v>3.0246</v>
+        <v>3.061100000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.8863</v>
+        <v>3.8823</v>
       </c>
       <c r="V25" t="n">
-        <v>2.1212</v>
+        <v>2.107499999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>10.5734</v>
+        <v>10.5227</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.452300000000001</v>
+        <v>-8.4152</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104539_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104539_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.5227</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.584</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104539_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.4152</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
